--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/4mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/20gps/4mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X61"/>
+  <dimension ref="A1:AC61"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.59653689815</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>612.7241775701281</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>610.0047056400032</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24">
+        <v>0.248141734</v>
+      </c>
+      <c r="Y2">
+        <v>0.261996876</v>
+      </c>
+      <c r="Z2">
+        <v>0.3608554879536767</v>
+      </c>
+      <c r="AA2">
+        <v>6.927571</v>
+      </c>
+      <c r="AB2">
+        <v>0.05304095355187641</v>
+      </c>
+      <c r="AC2">
+        <v>32.49947464260883</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.5966532176</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>618.223730498394</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24">
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>610.9029364763509</v>
+      </c>
+      <c r="X3">
+        <v>0.248162064</v>
+      </c>
+      <c r="Y3">
+        <v>0.26201311</v>
+      </c>
+      <c r="Z3">
+        <v>0.3608812544599846</v>
+      </c>
+      <c r="AA3">
+        <v>6.925522999999998</v>
+      </c>
+      <c r="AB3">
+        <v>0.0530597350912538</v>
+      </c>
+      <c r="AC3">
+        <v>32.80278736737147</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.59676953703</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>610.3772938189492</v>
       </c>
-      <c r="V4">
-        <v>4.027396063564406</v>
-      </c>
-      <c r="W4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24">
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.248203994</v>
+      </c>
+      <c r="Y4">
+        <v>0.262043668</v>
+      </c>
+      <c r="Z4">
+        <v>0.3609322742239134</v>
+      </c>
+      <c r="AA4">
+        <v>6.919837000000001</v>
+      </c>
+      <c r="AB4">
+        <v>0.05310902710871186</v>
+      </c>
+      <c r="AC4">
+        <v>32.41654424397275</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.59688585648</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>610.678164087046</v>
       </c>
-      <c r="V5">
-        <v>4.445834453936004</v>
-      </c>
-      <c r="W5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24">
+      <c r="V5" t="b">
+        <v>1</v>
+      </c>
+      <c r="W5">
+        <v>32.58811231863646</v>
+      </c>
+      <c r="X5">
+        <v>0.248244336</v>
+      </c>
+      <c r="Y5">
+        <v>0.262065314</v>
+      </c>
+      <c r="Z5">
+        <v>0.360975732090122</v>
+      </c>
+      <c r="AA5">
+        <v>6.910488999999998</v>
+      </c>
+      <c r="AB5">
+        <v>0.05318450017577969</v>
+      </c>
+      <c r="AC5">
+        <v>32.47861292523231</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.59700159722</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>610.5473782210314</v>
       </c>
-      <c r="V6">
-        <v>0.150862279802069</v>
-      </c>
-      <c r="W6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24">
+      <c r="V6" t="b">
+        <v>1</v>
+      </c>
+      <c r="X6">
+        <v>0.248286902</v>
+      </c>
+      <c r="Y6">
+        <v>0.262088552</v>
+      </c>
+      <c r="Z6">
+        <v>0.3610218757834687</v>
+      </c>
+      <c r="AA6">
+        <v>6.900825000000005</v>
+      </c>
+      <c r="AB6">
+        <v>0.05326291682720917</v>
+      </c>
+      <c r="AC6">
+        <v>32.51953422525742</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.59711733797</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>609.7763389378407</v>
       </c>
-      <c r="V7">
-        <v>0.487321782587917</v>
-      </c>
-      <c r="W7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24">
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>0.248304372</v>
+      </c>
+      <c r="Y7">
+        <v>0.26210192</v>
+      </c>
+      <c r="Z7">
+        <v>0.3610435951820788</v>
+      </c>
+      <c r="AA7">
+        <v>6.898774000000003</v>
+      </c>
+      <c r="AB7">
+        <v>0.05328128610549861</v>
+      </c>
+      <c r="AC7">
+        <v>32.48966757531058</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.59723365741</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>611.0016480797761</v>
       </c>
-      <c r="V8">
-        <v>0.6194413039310266</v>
-      </c>
-      <c r="W8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="X8">
+        <v>0.248302148</v>
+      </c>
+      <c r="Y8">
+        <v>0.262116564</v>
+      </c>
+      <c r="Z8">
+        <v>0.3610526967418745</v>
+      </c>
+      <c r="AA8">
+        <v>6.907207999999997</v>
+      </c>
+      <c r="AB8">
+        <v>0.05321981461159714</v>
+      </c>
+      <c r="AC8">
+        <v>32.517394438186</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.59734997685</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>608.7455322205144</v>
       </c>
-      <c r="V9">
-        <v>1.129454422291528</v>
-      </c>
-      <c r="W9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>0.248315172</v>
+      </c>
+      <c r="Y9">
+        <v>0.26213057</v>
+      </c>
+      <c r="Z9">
+        <v>0.3610718216282108</v>
+      </c>
+      <c r="AA9">
+        <v>6.907699000000001</v>
+      </c>
+      <c r="AB9">
+        <v>0.05321888462014956</v>
+      </c>
+      <c r="AC9">
+        <v>32.3967582422751</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.59746571759</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>611.6144363775693</v>
       </c>
-      <c r="V10">
-        <v>1.510859541822018</v>
-      </c>
-      <c r="W10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
+      <c r="V10" t="b">
+        <v>1</v>
+      </c>
+      <c r="X10">
+        <v>0.248342492</v>
+      </c>
+      <c r="Y10">
+        <v>0.262146168</v>
+      </c>
+      <c r="Z10">
+        <v>0.3611019339879728</v>
+      </c>
+      <c r="AA10">
+        <v>6.901838000000005</v>
+      </c>
+      <c r="AB10">
+        <v>0.05326676813987814</v>
+      </c>
+      <c r="AC10">
+        <v>32.57872437352624</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.59758203704</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>611.4989236917817</v>
       </c>
-      <c r="V11">
-        <v>1.624044274693521</v>
-      </c>
-      <c r="W11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24">
+      <c r="V11" t="b">
+        <v>1</v>
+      </c>
+      <c r="X11">
+        <v>0.248342492</v>
+      </c>
+      <c r="Y11">
+        <v>0.262162084</v>
+      </c>
+      <c r="Z11">
+        <v>0.3611134885600275</v>
+      </c>
+      <c r="AA11">
+        <v>6.909796</v>
+      </c>
+      <c r="AB11">
+        <v>0.05320922663499334</v>
+      </c>
+      <c r="AC11">
+        <v>32.53738481777051</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.59769835648</v>
       </c>
@@ -1269,14 +1470,29 @@
       <c r="U12">
         <v>609.4123491725514</v>
       </c>
-      <c r="V12">
-        <v>1.239376487282959</v>
-      </c>
-      <c r="W12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
+      <c r="V12" t="b">
+        <v>1</v>
+      </c>
+      <c r="X12">
+        <v>0.24836441</v>
+      </c>
+      <c r="Y12">
+        <v>0.262173544</v>
+      </c>
+      <c r="Z12">
+        <v>0.361136881705771</v>
+      </c>
+      <c r="AA12">
+        <v>6.904567</v>
+      </c>
+      <c r="AB12">
+        <v>0.05325142831602377</v>
+      </c>
+      <c r="AC12">
+        <v>32.45207802686177</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29">
       <c r="A13" s="1">
         <v>46068.59781409722</v>
       </c>
@@ -1340,14 +1556,29 @@
       <c r="U13">
         <v>611.3219006911818</v>
       </c>
-      <c r="V13">
-        <v>1.156972872725952</v>
-      </c>
-      <c r="W13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
+      <c r="V13" t="b">
+        <v>1</v>
+      </c>
+      <c r="X13">
+        <v>0.248374576</v>
+      </c>
+      <c r="Y13">
+        <v>0.262177044</v>
+      </c>
+      <c r="Z13">
+        <v>0.3611464140812666</v>
+      </c>
+      <c r="AA13">
+        <v>6.901233999999995</v>
+      </c>
+      <c r="AB13">
+        <v>0.05327759645269706</v>
+      </c>
+      <c r="AC13">
+        <v>32.56976152772053</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29">
       <c r="A14" s="1">
         <v>46068.59792983796</v>
       </c>
@@ -1411,14 +1642,29 @@
       <c r="U14">
         <v>613.6504413861016</v>
       </c>
-      <c r="V14">
-        <v>2.122495166101912</v>
-      </c>
-      <c r="W14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24">
+      <c r="V14" t="b">
+        <v>1</v>
+      </c>
+      <c r="X14">
+        <v>0.24836854</v>
+      </c>
+      <c r="Y14">
+        <v>0.26218564</v>
+      </c>
+      <c r="Z14">
+        <v>0.3611485033666084</v>
+      </c>
+      <c r="AA14">
+        <v>6.908550000000005</v>
+      </c>
+      <c r="AB14">
+        <v>0.05322346238016791</v>
+      </c>
+      <c r="AC14">
+        <v>32.66060118168662</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29">
       <c r="A15" s="1">
         <v>46068.59804615741</v>
       </c>
@@ -1482,14 +1728,29 @@
       <c r="U15">
         <v>610.4233086558618</v>
       </c>
-      <c r="V15">
-        <v>1.665530699828399</v>
-      </c>
-      <c r="W15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24">
+      <c r="V15" t="b">
+        <v>1</v>
+      </c>
+      <c r="X15">
+        <v>0.248380294</v>
+      </c>
+      <c r="Y15">
+        <v>0.262192006</v>
+      </c>
+      <c r="Z15">
+        <v>0.3611612084067591</v>
+      </c>
+      <c r="AA15">
+        <v>6.905856</v>
+      </c>
+      <c r="AB15">
+        <v>0.05324529924344301</v>
+      </c>
+      <c r="AC15">
+        <v>32.50217173455394</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29">
       <c r="A16" s="1">
         <v>46068.59816189815</v>
       </c>
@@ -1553,14 +1814,29 @@
       <c r="U16">
         <v>608.2147839677289</v>
       </c>
-      <c r="V16">
-        <v>2.733689159560322</v>
-      </c>
-      <c r="W16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23">
+      <c r="V16" t="b">
+        <v>1</v>
+      </c>
+      <c r="X16">
+        <v>0.2484038</v>
+      </c>
+      <c r="Y16">
+        <v>0.262199328</v>
+      </c>
+      <c r="Z16">
+        <v>0.3611826898649652</v>
+      </c>
+      <c r="AA16">
+        <v>6.897763999999995</v>
+      </c>
+      <c r="AB16">
+        <v>0.05330862006210418</v>
+      </c>
+      <c r="AC16">
+        <v>32.42309083469043</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29">
       <c r="A17" s="1">
         <v>46068.59827821759</v>
       </c>
@@ -1624,14 +1900,29 @@
       <c r="U17">
         <v>610.612717186484</v>
       </c>
-      <c r="V17">
-        <v>1.333137940547678</v>
-      </c>
-      <c r="W17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23">
+      <c r="V17" t="b">
+        <v>1</v>
+      </c>
+      <c r="X17">
+        <v>0.248402848</v>
+      </c>
+      <c r="Y17">
+        <v>0.262205694</v>
+      </c>
+      <c r="Z17">
+        <v>0.3611866565372159</v>
+      </c>
+      <c r="AA17">
+        <v>6.901422999999994</v>
+      </c>
+      <c r="AB17">
+        <v>0.05328191622218861</v>
+      </c>
+      <c r="AC17">
+        <v>32.53461564133319</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29">
       <c r="A18" s="1">
         <v>46068.59839395833</v>
       </c>
@@ -1695,14 +1986,29 @@
       <c r="U18">
         <v>614.0811201972535</v>
       </c>
-      <c r="V18">
-        <v>2.949401180029531</v>
-      </c>
-      <c r="W18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23">
+      <c r="V18" t="b">
+        <v>1</v>
+      </c>
+      <c r="X18">
+        <v>0.248395224</v>
+      </c>
+      <c r="Y18">
+        <v>0.262208878</v>
+      </c>
+      <c r="Z18">
+        <v>0.361183724727498</v>
+      </c>
+      <c r="AA18">
+        <v>6.906827</v>
+      </c>
+      <c r="AB18">
+        <v>0.05324127976231228</v>
+      </c>
+      <c r="AC18">
+        <v>32.69446471717609</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29">
       <c r="A19" s="1">
         <v>46068.59851027778</v>
       </c>
@@ -1766,14 +2072,29 @@
       <c r="U19">
         <v>612.2676734537313</v>
       </c>
-      <c r="V19">
-        <v>1.734804925787288</v>
-      </c>
-      <c r="W19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23">
+      <c r="V19" t="b">
+        <v>1</v>
+      </c>
+      <c r="X19">
+        <v>0.248380928</v>
+      </c>
+      <c r="Y19">
+        <v>0.262207922</v>
+      </c>
+      <c r="Z19">
+        <v>0.3611731991077124</v>
+      </c>
+      <c r="AA19">
+        <v>6.913497</v>
+      </c>
+      <c r="AB19">
+        <v>0.05319023127535726</v>
+      </c>
+      <c r="AC19">
+        <v>32.56665915342889</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29">
       <c r="A20" s="1">
         <v>46068.59862601852</v>
       </c>
@@ -1837,14 +2158,29 @@
       <c r="U20">
         <v>611.7244894881495</v>
       </c>
-      <c r="V20">
-        <v>1.234054713208922</v>
-      </c>
-      <c r="W20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23">
+      <c r="V20" t="b">
+        <v>1</v>
+      </c>
+      <c r="X20">
+        <v>0.248382834</v>
+      </c>
+      <c r="Y20">
+        <v>0.262226386</v>
+      </c>
+      <c r="Z20">
+        <v>0.3611879147209837</v>
+      </c>
+      <c r="AA20">
+        <v>6.921776000000001</v>
+      </c>
+      <c r="AB20">
+        <v>0.05313094946077741</v>
+      </c>
+      <c r="AC20">
+        <v>32.50150293491473</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29">
       <c r="A21" s="1">
         <v>46068.59874233796</v>
       </c>
@@ -1908,14 +2244,29 @@
       <c r="U21">
         <v>612.7444362062556</v>
       </c>
-      <c r="V21">
-        <v>0.5103336899262786</v>
-      </c>
-      <c r="W21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23">
+      <c r="V21" t="b">
+        <v>1</v>
+      </c>
+      <c r="X21">
+        <v>0.2483876</v>
+      </c>
+      <c r="Y21">
+        <v>0.262221928</v>
+      </c>
+      <c r="Z21">
+        <v>0.3611879557208368</v>
+      </c>
+      <c r="AA21">
+        <v>6.917164</v>
+      </c>
+      <c r="AB21">
+        <v>0.05316512568630083</v>
+      </c>
+      <c r="AC21">
+        <v>32.57663496448712</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29">
       <c r="A22" s="1">
         <v>46068.59885865741</v>
       </c>
@@ -1979,14 +2330,29 @@
       <c r="U22">
         <v>613.4240892546039</v>
       </c>
-      <c r="V22">
-        <v>0.8554588378999429</v>
-      </c>
-      <c r="W22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23">
+      <c r="V22" t="b">
+        <v>1</v>
+      </c>
+      <c r="X22">
+        <v>0.24840666</v>
+      </c>
+      <c r="Y22">
+        <v>0.262227022</v>
+      </c>
+      <c r="Z22">
+        <v>0.3612047615956137</v>
+      </c>
+      <c r="AA22">
+        <v>6.910181000000001</v>
+      </c>
+      <c r="AB22">
+        <v>0.05321933995806756</v>
+      </c>
+      <c r="AC22">
+        <v>32.64602514450874</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29">
       <c r="A23" s="1">
         <v>46068.59897439815</v>
       </c>
@@ -2050,14 +2416,29 @@
       <c r="U23">
         <v>610.3147374195049</v>
       </c>
-      <c r="V23">
-        <v>1.634698407194601</v>
-      </c>
-      <c r="W23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23">
+      <c r="V23" t="b">
+        <v>1</v>
+      </c>
+      <c r="X23">
+        <v>0.248410472</v>
+      </c>
+      <c r="Y23">
+        <v>0.262221928</v>
+      </c>
+      <c r="Z23">
+        <v>0.3612036850909746</v>
+      </c>
+      <c r="AA23">
+        <v>6.905728000000003</v>
+      </c>
+      <c r="AB23">
+        <v>0.05325229285006259</v>
+      </c>
+      <c r="AC23">
+        <v>32.50065912777253</v>
+      </c>
+    </row>
+    <row r="24" spans="1:29">
       <c r="A24" s="1">
         <v>46068.59909071759</v>
       </c>
@@ -2121,14 +2502,29 @@
       <c r="U24">
         <v>613.7735209894797</v>
       </c>
-      <c r="V24">
-        <v>1.90409012197904</v>
-      </c>
-      <c r="W24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23">
+      <c r="V24" t="b">
+        <v>1</v>
+      </c>
+      <c r="X24">
+        <v>0.248408882</v>
+      </c>
+      <c r="Y24">
+        <v>0.262227658</v>
+      </c>
+      <c r="Z24">
+        <v>0.3612067514272884</v>
+      </c>
+      <c r="AA24">
+        <v>6.909388</v>
+      </c>
+      <c r="AB24">
+        <v>0.05322551523087925</v>
+      </c>
+      <c r="AC24">
+        <v>32.66841188973594</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29">
       <c r="A25" s="1">
         <v>46068.59920703703</v>
       </c>
@@ -2192,14 +2588,29 @@
       <c r="U25">
         <v>613.9957625717719</v>
       </c>
-      <c r="V25">
-        <v>2.064078538414533</v>
-      </c>
-      <c r="W25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23">
+      <c r="V25" t="b">
+        <v>1</v>
+      </c>
+      <c r="X25">
+        <v>0.248401576</v>
+      </c>
+      <c r="Y25">
+        <v>0.26222161</v>
+      </c>
+      <c r="Z25">
+        <v>0.3611973362447125</v>
+      </c>
+      <c r="AA25">
+        <v>6.910016999999996</v>
+      </c>
+      <c r="AB25">
+        <v>0.05321950301464054</v>
+      </c>
+      <c r="AC25">
+        <v>32.67654933716494</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29">
       <c r="A26" s="1">
         <v>46068.59932277778</v>
       </c>
@@ -2263,14 +2674,29 @@
       <c r="U26">
         <v>611.853710104471</v>
       </c>
-      <c r="V26">
-        <v>1.177812515342378</v>
-      </c>
-      <c r="W26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23">
+      <c r="V26" t="b">
+        <v>1</v>
+      </c>
+      <c r="X26">
+        <v>0.248401576</v>
+      </c>
+      <c r="Y26">
+        <v>0.262225112</v>
+      </c>
+      <c r="Z26">
+        <v>0.3611998786305116</v>
+      </c>
+      <c r="AA26">
+        <v>6.911767999999995</v>
+      </c>
+      <c r="AB26">
+        <v>0.05320685795454673</v>
+      </c>
+      <c r="AC26">
+        <v>32.554813442491</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29">
       <c r="A27" s="1">
         <v>46068.59943909722</v>
       </c>
@@ -2334,14 +2760,29 @@
       <c r="U27">
         <v>612.8527876743411</v>
       </c>
-      <c r="V27">
-        <v>1.071831483914099</v>
-      </c>
-      <c r="W27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23">
+      <c r="V27" t="b">
+        <v>1</v>
+      </c>
+      <c r="X27">
+        <v>0.248408882</v>
+      </c>
+      <c r="Y27">
+        <v>0.262220336</v>
+      </c>
+      <c r="Z27">
+        <v>0.3612014358615464</v>
+      </c>
+      <c r="AA27">
+        <v>6.905726999999999</v>
+      </c>
+      <c r="AB27">
+        <v>0.0532519803788089</v>
+      </c>
+      <c r="AC27">
+        <v>32.63562462433235</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29">
       <c r="A28" s="1">
         <v>46068.59955483797</v>
       </c>
@@ -2405,14 +2846,29 @@
       <c r="U28">
         <v>612.4102559958144</v>
       </c>
-      <c r="V28">
-        <v>0.5006218809800955</v>
-      </c>
-      <c r="W28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23">
+      <c r="V28" t="b">
+        <v>1</v>
+      </c>
+      <c r="X28">
+        <v>0.248413648</v>
+      </c>
+      <c r="Y28">
+        <v>0.26221779</v>
+      </c>
+      <c r="Z28">
+        <v>0.3612028653058444</v>
+      </c>
+      <c r="AA28">
+        <v>6.902070999999999</v>
+      </c>
+      <c r="AB28">
+        <v>0.05327939672410623</v>
+      </c>
+      <c r="AC28">
+        <v>32.62884898711246</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29">
       <c r="A29" s="1">
         <v>46068.5996711574</v>
       </c>
@@ -2476,14 +2932,29 @@
       <c r="U29">
         <v>612.3836483278935</v>
       </c>
-      <c r="V29">
-        <v>0.2635128019933831</v>
-      </c>
-      <c r="W29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23">
+      <c r="V29" t="b">
+        <v>1</v>
+      </c>
+      <c r="X29">
+        <v>0.248410788</v>
+      </c>
+      <c r="Y29">
+        <v>0.262207604</v>
+      </c>
+      <c r="Z29">
+        <v>0.3611935038039883</v>
+      </c>
+      <c r="AA29">
+        <v>6.898408000000003</v>
+      </c>
+      <c r="AB29">
+        <v>0.05330535833905431</v>
+      </c>
+      <c r="AC29">
+        <v>32.64332981509578</v>
+      </c>
+    </row>
+    <row r="30" spans="1:29">
       <c r="A30" s="1">
         <v>46068.59978747685</v>
       </c>
@@ -2547,14 +3018,29 @@
       <c r="U30">
         <v>610.9635360583143</v>
       </c>
-      <c r="V30">
-        <v>0.827690099389667</v>
-      </c>
-      <c r="W30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23">
+      <c r="V30" t="b">
+        <v>1</v>
+      </c>
+      <c r="X30">
+        <v>0.248410154</v>
+      </c>
+      <c r="Y30">
+        <v>0.262211424</v>
+      </c>
+      <c r="Z30">
+        <v>0.3611958409040883</v>
+      </c>
+      <c r="AA30">
+        <v>6.900634999999994</v>
+      </c>
+      <c r="AB30">
+        <v>0.05328909360616521</v>
+      </c>
+      <c r="AC30">
+        <v>32.55769306296521</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29">
       <c r="A31" s="1">
         <v>46068.59990321759</v>
       </c>
@@ -2618,14 +3104,29 @@
       <c r="U31">
         <v>612.4221270764353</v>
       </c>
-      <c r="V31">
-        <v>0.8312327422214912</v>
-      </c>
-      <c r="W31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23">
+      <c r="V31" t="b">
+        <v>1</v>
+      </c>
+      <c r="X31">
+        <v>0.248401576</v>
+      </c>
+      <c r="Y31">
+        <v>0.26219901</v>
+      </c>
+      <c r="Z31">
+        <v>0.3611809294581649</v>
+      </c>
+      <c r="AA31">
+        <v>6.898716999999998</v>
+      </c>
+      <c r="AB31">
+        <v>0.05330126442772894</v>
+      </c>
+      <c r="AC31">
+        <v>32.6428737366933</v>
+      </c>
+    </row>
+    <row r="32" spans="1:29">
       <c r="A32" s="1">
         <v>46068.60001953704</v>
       </c>
@@ -2689,14 +3190,29 @@
       <c r="U32">
         <v>612.7110345977513</v>
       </c>
-      <c r="V32">
-        <v>0.9367235859950099</v>
-      </c>
-      <c r="W32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23">
+      <c r="V32" t="b">
+        <v>1</v>
+      </c>
+      <c r="X32">
+        <v>0.248392046</v>
+      </c>
+      <c r="Y32">
+        <v>0.262190414</v>
+      </c>
+      <c r="Z32">
+        <v>0.3611681349587163</v>
+      </c>
+      <c r="AA32">
+        <v>6.899184000000005</v>
+      </c>
+      <c r="AB32">
+        <v>0.05329596194839346</v>
+      </c>
+      <c r="AC32">
+        <v>32.65502398528254</v>
+      </c>
+    </row>
+    <row r="33" spans="1:29">
       <c r="A33" s="1">
         <v>46068.60013585648</v>
       </c>
@@ -2760,14 +3276,29 @@
       <c r="U33">
         <v>610.1847444353468</v>
       </c>
-      <c r="V33">
-        <v>1.38272018277872</v>
-      </c>
-      <c r="W33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23">
+      <c r="V33" t="b">
+        <v>1</v>
+      </c>
+      <c r="X33">
+        <v>0.248394588</v>
+      </c>
+      <c r="Y33">
+        <v>0.262189778</v>
+      </c>
+      <c r="Z33">
+        <v>0.3611694215120917</v>
+      </c>
+      <c r="AA33">
+        <v>6.897595000000003</v>
+      </c>
+      <c r="AB33">
+        <v>0.05330799075908839</v>
+      </c>
+      <c r="AC33">
+        <v>32.52772271769618</v>
+      </c>
+    </row>
+    <row r="34" spans="1:29">
       <c r="A34" s="1">
         <v>46068.60025217593</v>
       </c>
@@ -2831,14 +3362,29 @@
       <c r="U34">
         <v>610.6222806508694</v>
       </c>
-      <c r="V34">
-        <v>1.350090921331357</v>
-      </c>
-      <c r="W34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23">
+      <c r="V34" t="b">
+        <v>1</v>
+      </c>
+      <c r="X34">
+        <v>0.24842699</v>
+      </c>
+      <c r="Y34">
+        <v>0.262201874</v>
+      </c>
+      <c r="Z34">
+        <v>0.3612004873883367</v>
+      </c>
+      <c r="AA34">
+        <v>6.887442</v>
+      </c>
+      <c r="AB34">
+        <v>0.05338824111000229</v>
+      </c>
+      <c r="AC34">
+        <v>32.6000495465281</v>
+      </c>
+    </row>
+    <row r="35" spans="1:29">
       <c r="A35" s="1">
         <v>46068.60036849537</v>
       </c>
@@ -2902,14 +3448,29 @@
       <c r="U35">
         <v>609.78998555761</v>
       </c>
-      <c r="V35">
-        <v>0.4163307246446029</v>
-      </c>
-      <c r="W35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:23">
+      <c r="V35" t="b">
+        <v>1</v>
+      </c>
+      <c r="X35">
+        <v>0.248447002</v>
+      </c>
+      <c r="Y35">
+        <v>0.262206648</v>
+      </c>
+      <c r="Z35">
+        <v>0.3612177169771493</v>
+      </c>
+      <c r="AA35">
+        <v>6.879823000000002</v>
+      </c>
+      <c r="AB35">
+        <v>0.0534477523812549</v>
+      </c>
+      <c r="AC35">
+        <v>32.59190415265213</v>
+      </c>
+    </row>
+    <row r="36" spans="1:29">
       <c r="A36" s="1">
         <v>46068.60048481481</v>
       </c>
@@ -2973,14 +3534,29 @@
       <c r="U36">
         <v>612.5729485725396</v>
       </c>
-      <c r="V36">
-        <v>1.428443418863102</v>
-      </c>
-      <c r="W36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:23">
+      <c r="V36" t="b">
+        <v>1</v>
+      </c>
+      <c r="X36">
+        <v>0.248430802</v>
+      </c>
+      <c r="Y36">
+        <v>0.262204102</v>
+      </c>
+      <c r="Z36">
+        <v>0.3612047265582077</v>
+      </c>
+      <c r="AA36">
+        <v>6.886650000000003</v>
+      </c>
+      <c r="AB36">
+        <v>0.05339477030150349</v>
+      </c>
+      <c r="AC36">
+        <v>32.70819188194547</v>
+      </c>
+    </row>
+    <row r="37" spans="1:29">
       <c r="A37" s="1">
         <v>46068.60060113426</v>
       </c>
@@ -3044,14 +3620,29 @@
       <c r="U37">
         <v>607.9380558581354</v>
       </c>
-      <c r="V37">
-        <v>2.332979397976191</v>
-      </c>
-      <c r="W37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:23">
+      <c r="V37" t="b">
+        <v>1</v>
+      </c>
+      <c r="X37">
+        <v>0.248438426</v>
+      </c>
+      <c r="Y37">
+        <v>0.262216198</v>
+      </c>
+      <c r="Z37">
+        <v>0.3612187509071653</v>
+      </c>
+      <c r="AA37">
+        <v>6.888885999999999</v>
+      </c>
+      <c r="AB37">
+        <v>0.0533800471193901</v>
+      </c>
+      <c r="AC37">
+        <v>32.45176206737768</v>
+      </c>
+    </row>
+    <row r="38" spans="1:29">
       <c r="A38" s="1">
         <v>46068.600716875</v>
       </c>
@@ -3115,14 +3706,29 @@
       <c r="U38">
         <v>610.7347901376331</v>
       </c>
-      <c r="V38">
-        <v>2.333908722007075</v>
-      </c>
-      <c r="W38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:23">
+      <c r="V38" t="b">
+        <v>1</v>
+      </c>
+      <c r="X38">
+        <v>0.24844732</v>
+      </c>
+      <c r="Y38">
+        <v>0.262220336</v>
+      </c>
+      <c r="Z38">
+        <v>0.361227871885788</v>
+      </c>
+      <c r="AA38">
+        <v>6.886507999999999</v>
+      </c>
+      <c r="AB38">
+        <v>0.05339913418911856</v>
+      </c>
+      <c r="AC38">
+        <v>32.61270901252263</v>
+      </c>
+    </row>
+    <row r="39" spans="1:29">
       <c r="A39" s="1">
         <v>46068.60083319445</v>
       </c>
@@ -3186,14 +3792,29 @@
       <c r="U39">
         <v>611.2026361736201</v>
       </c>
-      <c r="V39">
-        <v>1.76531806292538</v>
-      </c>
-      <c r="W39" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:23">
+      <c r="V39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X39">
+        <v>0.248453992</v>
+      </c>
+      <c r="Y39">
+        <v>0.26221588</v>
+      </c>
+      <c r="Z39">
+        <v>0.3612292262053425</v>
+      </c>
+      <c r="AA39">
+        <v>6.880944</v>
+      </c>
+      <c r="AB39">
+        <v>0.05344099292208584</v>
+      </c>
+      <c r="AC39">
+        <v>32.66327575371464</v>
+      </c>
+    </row>
+    <row r="40" spans="1:29">
       <c r="A40" s="1">
         <v>46068.60094893519</v>
       </c>
@@ -3257,14 +3878,29 @@
       <c r="U40">
         <v>612.468480767453</v>
       </c>
-      <c r="V40">
-        <v>0.896932331993314</v>
-      </c>
-      <c r="W40" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:23">
+      <c r="V40" t="b">
+        <v>1</v>
+      </c>
+      <c r="X40">
+        <v>0.248465426</v>
+      </c>
+      <c r="Y40">
+        <v>0.26221779</v>
+      </c>
+      <c r="Z40">
+        <v>0.3612384770616851</v>
+      </c>
+      <c r="AA40">
+        <v>6.876182</v>
+      </c>
+      <c r="AB40">
+        <v>0.05347802886739016</v>
+      </c>
+      <c r="AC40">
+        <v>32.75360709484845</v>
+      </c>
+    </row>
+    <row r="41" spans="1:29">
       <c r="A41" s="1">
         <v>46068.60106525463</v>
       </c>
@@ -3328,14 +3964,29 @@
       <c r="U41">
         <v>611.346950964225</v>
       </c>
-      <c r="V41">
-        <v>0.6929428059676157</v>
-      </c>
-      <c r="W41" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:23">
+      <c r="V41" t="b">
+        <v>1</v>
+      </c>
+      <c r="X41">
+        <v>0.24847305</v>
+      </c>
+      <c r="Y41">
+        <v>0.262218426</v>
+      </c>
+      <c r="Z41">
+        <v>0.361244182666268</v>
+      </c>
+      <c r="AA41">
+        <v>6.872687999999997</v>
+      </c>
+      <c r="AB41">
+        <v>0.05350508165616751</v>
+      </c>
+      <c r="AC41">
+        <v>32.71016853158989</v>
+      </c>
+    </row>
+    <row r="42" spans="1:29">
       <c r="A42" s="1">
         <v>46068.60118099537</v>
       </c>
@@ -3399,14 +4050,29 @@
       <c r="U42">
         <v>608.0137608294481</v>
       </c>
-      <c r="V42">
-        <v>2.31705687241927</v>
-      </c>
-      <c r="W42" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:23">
+      <c r="V42" t="b">
+        <v>1</v>
+      </c>
+      <c r="X42">
+        <v>0.24848131</v>
+      </c>
+      <c r="Y42">
+        <v>0.262206012</v>
+      </c>
+      <c r="Z42">
+        <v>0.3612408533766083</v>
+      </c>
+      <c r="AA42">
+        <v>6.862351000000004</v>
+      </c>
+      <c r="AB42">
+        <v>0.05358238833935218</v>
+      </c>
+      <c r="AC42">
+        <v>32.57882944843348</v>
+      </c>
+    </row>
+    <row r="43" spans="1:29">
       <c r="A43" s="1">
         <v>46068.60129731482</v>
       </c>
@@ -3470,14 +4136,29 @@
       <c r="U43">
         <v>607.8852395330144</v>
       </c>
-      <c r="V43">
-        <v>1.962571452251669</v>
-      </c>
-      <c r="W43" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:23">
+      <c r="V43" t="b">
+        <v>1</v>
+      </c>
+      <c r="X43">
+        <v>0.248489888</v>
+      </c>
+      <c r="Y43">
+        <v>0.262195508</v>
+      </c>
+      <c r="Z43">
+        <v>0.361239129737672</v>
+      </c>
+      <c r="AA43">
+        <v>6.852810000000005</v>
+      </c>
+      <c r="AB43">
+        <v>0.05365414603491477</v>
+      </c>
+      <c r="AC43">
+        <v>32.6155634143735</v>
+      </c>
+    </row>
+    <row r="44" spans="1:29">
       <c r="A44" s="1">
         <v>46068.60141363426</v>
       </c>
@@ -3541,14 +4222,29 @@
       <c r="U44">
         <v>605.9468397614678</v>
       </c>
-      <c r="V44">
-        <v>1.158020876264238</v>
-      </c>
-      <c r="W44" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:23">
+      <c r="V44" t="b">
+        <v>1</v>
+      </c>
+      <c r="X44">
+        <v>0.24847591</v>
+      </c>
+      <c r="Y44">
+        <v>0.262196462</v>
+      </c>
+      <c r="Z44">
+        <v>0.3612302071195674</v>
+      </c>
+      <c r="AA44">
+        <v>6.860275999999999</v>
+      </c>
+      <c r="AB44">
+        <v>0.05359650616300242</v>
+      </c>
+      <c r="AC44">
+        <v>32.47663353172735</v>
+      </c>
+    </row>
+    <row r="45" spans="1:29">
       <c r="A45" s="1">
         <v>46068.601529375</v>
       </c>
@@ -3612,14 +4308,29 @@
       <c r="U45">
         <v>611.8668942402169</v>
       </c>
-      <c r="V45">
-        <v>3.018222791452121</v>
-      </c>
-      <c r="W45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:23">
+      <c r="V45" t="b">
+        <v>1</v>
+      </c>
+      <c r="X45">
+        <v>0.248460026</v>
+      </c>
+      <c r="Y45">
+        <v>0.26218564</v>
+      </c>
+      <c r="Z45">
+        <v>0.3612114260957566</v>
+      </c>
+      <c r="AA45">
+        <v>6.862807000000004</v>
+      </c>
+      <c r="AB45">
+        <v>0.05357473947671999</v>
+      </c>
+      <c r="AC45">
+        <v>32.78060945334941</v>
+      </c>
+    </row>
+    <row r="46" spans="1:29">
       <c r="A46" s="1">
         <v>46068.60164569444</v>
       </c>
@@ -3683,14 +4394,29 @@
       <c r="U46">
         <v>606.1654411071078</v>
       </c>
-      <c r="V46">
-        <v>3.356620309395403</v>
-      </c>
-      <c r="W46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:23">
+      <c r="V46" t="b">
+        <v>1</v>
+      </c>
+      <c r="X46">
+        <v>0.24845558</v>
+      </c>
+      <c r="Y46">
+        <v>0.26218182</v>
+      </c>
+      <c r="Z46">
+        <v>0.3612055951555136</v>
+      </c>
+      <c r="AA46">
+        <v>6.863120000000002</v>
+      </c>
+      <c r="AB46">
+        <v>0.05357154659888809</v>
+      </c>
+      <c r="AC46">
+        <v>32.47322017490498</v>
+      </c>
+    </row>
+    <row r="47" spans="1:29">
       <c r="A47" s="1">
         <v>46068.60176143519</v>
       </c>
@@ -3754,14 +4480,29 @@
       <c r="U47">
         <v>607.1802632790585</v>
       </c>
-      <c r="V47">
-        <v>3.041407065701055</v>
-      </c>
-      <c r="W47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="1:23">
+      <c r="V47" t="b">
+        <v>1</v>
+      </c>
+      <c r="X47">
+        <v>0.248434296</v>
+      </c>
+      <c r="Y47">
+        <v>0.262171634</v>
+      </c>
+      <c r="Z47">
+        <v>0.3611835615075049</v>
+      </c>
+      <c r="AA47">
+        <v>6.868668999999997</v>
+      </c>
+      <c r="AB47">
+        <v>0.05352662492655559</v>
+      </c>
+      <c r="AC47">
+        <v>32.50031021534544</v>
+      </c>
+    </row>
+    <row r="48" spans="1:29">
       <c r="A48" s="1">
         <v>46068.60187775463</v>
       </c>
@@ -3825,14 +4566,29 @@
       <c r="U48">
         <v>610.2957966162572</v>
       </c>
-      <c r="V48">
-        <v>2.15237266939687</v>
-      </c>
-      <c r="W48" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:23">
+      <c r="V48" t="b">
+        <v>1</v>
+      </c>
+      <c r="X48">
+        <v>0.24842</v>
+      </c>
+      <c r="Y48">
+        <v>0.262175772</v>
+      </c>
+      <c r="Z48">
+        <v>0.3611767321184962</v>
+      </c>
+      <c r="AA48">
+        <v>6.877885999999997</v>
+      </c>
+      <c r="AB48">
+        <v>0.05345642412416425</v>
+      </c>
+      <c r="AC48">
+        <v>32.62423094511333</v>
+      </c>
+    </row>
+    <row r="49" spans="1:29">
       <c r="A49" s="1">
         <v>46068.60199407407</v>
       </c>
@@ -3896,14 +4652,29 @@
       <c r="U49">
         <v>612.6608935175793</v>
       </c>
-      <c r="V49">
-        <v>2.748864588007736</v>
-      </c>
-      <c r="W49" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:23">
+      <c r="V49" t="b">
+        <v>1</v>
+      </c>
+      <c r="X49">
+        <v>0.248424766</v>
+      </c>
+      <c r="Y49">
+        <v>0.262174498</v>
+      </c>
+      <c r="Z49">
+        <v>0.3611790854461354</v>
+      </c>
+      <c r="AA49">
+        <v>6.874865999999997</v>
+      </c>
+      <c r="AB49">
+        <v>0.05347942122060159</v>
+      </c>
+      <c r="AC49">
+        <v>32.76474998981676</v>
+      </c>
+    </row>
+    <row r="50" spans="1:29">
       <c r="A50" s="1">
         <v>46068.60211039352</v>
       </c>
@@ -3967,14 +4738,29 @@
       <c r="U50">
         <v>612.6350636987997</v>
       </c>
-      <c r="V50">
-        <v>1.358094315309986</v>
-      </c>
-      <c r="W50" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:23">
+      <c r="V50" t="b">
+        <v>1</v>
+      </c>
+      <c r="X50">
+        <v>0.24843112</v>
+      </c>
+      <c r="Y50">
+        <v>0.262172588</v>
+      </c>
+      <c r="Z50">
+        <v>0.3611820694373852</v>
+      </c>
+      <c r="AA50">
+        <v>6.870733999999999</v>
+      </c>
+      <c r="AB50">
+        <v>0.05351088573299894</v>
+      </c>
+      <c r="AC50">
+        <v>32.782644889615</v>
+      </c>
+    </row>
+    <row r="51" spans="1:29">
       <c r="A51" s="1">
         <v>46068.60222613426</v>
       </c>
@@ -4038,14 +4824,29 @@
       <c r="U51">
         <v>609.4685518139369</v>
       </c>
-      <c r="V51">
-        <v>1.835688347248429</v>
-      </c>
-      <c r="W51" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:23">
+      <c r="V51" t="b">
+        <v>1</v>
+      </c>
+      <c r="X51">
+        <v>0.248416506</v>
+      </c>
+      <c r="Y51">
+        <v>0.262171952</v>
+      </c>
+      <c r="Z51">
+        <v>0.3611715560073057</v>
+      </c>
+      <c r="AA51">
+        <v>6.877723000000003</v>
+      </c>
+      <c r="AB51">
+        <v>0.05345690738578206</v>
+      </c>
+      <c r="AC51">
+        <v>32.58030392886434</v>
+      </c>
+    </row>
+    <row r="52" spans="1:29">
       <c r="A52" s="1">
         <v>46068.602341875</v>
       </c>
@@ -4109,14 +4910,29 @@
       <c r="U52">
         <v>611.8230049698807</v>
       </c>
-      <c r="V52">
-        <v>1.644672538822047</v>
-      </c>
-      <c r="W52" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:23">
+      <c r="V52" t="b">
+        <v>1</v>
+      </c>
+      <c r="X52">
+        <v>0.248408248</v>
+      </c>
+      <c r="Y52">
+        <v>0.262171634</v>
+      </c>
+      <c r="Z52">
+        <v>0.361165645305114</v>
+      </c>
+      <c r="AA52">
+        <v>6.881692999999999</v>
+      </c>
+      <c r="AB52">
+        <v>0.05342630422542917</v>
+      </c>
+      <c r="AC52">
+        <v>32.68744199563711</v>
+      </c>
+    </row>
+    <row r="53" spans="1:29">
       <c r="A53" s="1">
         <v>46068.60245819444</v>
       </c>
@@ -4180,14 +4996,29 @@
       <c r="U53">
         <v>609.2205228749367</v>
       </c>
-      <c r="V53">
-        <v>1.43630782869415</v>
-      </c>
-      <c r="W53" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="54" spans="1:23">
+      <c r="V53" t="b">
+        <v>1</v>
+      </c>
+      <c r="X53">
+        <v>0.248421906</v>
+      </c>
+      <c r="Y53">
+        <v>0.262178318</v>
+      </c>
+      <c r="Z53">
+        <v>0.3611798912037905</v>
+      </c>
+      <c r="AA53">
+        <v>6.878205999999999</v>
+      </c>
+      <c r="AB53">
+        <v>0.05345447534409882</v>
+      </c>
+      <c r="AC53">
+        <v>32.5655634191373</v>
+      </c>
+    </row>
+    <row r="54" spans="1:29">
       <c r="A54" s="1">
         <v>46068.60257451389</v>
       </c>
@@ -4251,14 +5082,29 @@
       <c r="U54">
         <v>609.3984701157509</v>
       </c>
-      <c r="V54">
-        <v>1.453899786430543</v>
-      </c>
-      <c r="W54" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="55" spans="1:23">
+      <c r="V54" t="b">
+        <v>1</v>
+      </c>
+      <c r="X54">
+        <v>0.248432072</v>
+      </c>
+      <c r="Y54">
+        <v>0.262177044</v>
+      </c>
+      <c r="Z54">
+        <v>0.3611859587508782</v>
+      </c>
+      <c r="AA54">
+        <v>6.872485999999995</v>
+      </c>
+      <c r="AB54">
+        <v>0.05349827664132137</v>
+      </c>
+      <c r="AC54">
+        <v>32.60176793905045</v>
+      </c>
+    </row>
+    <row r="55" spans="1:29">
       <c r="A55" s="1">
         <v>46068.60269025463</v>
       </c>
@@ -4322,14 +5168,29 @@
       <c r="U55">
         <v>608.0364195725931</v>
       </c>
-      <c r="V55">
-        <v>0.7403768784907376</v>
-      </c>
-      <c r="W55" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="56" spans="1:23">
+      <c r="V55" t="b">
+        <v>1</v>
+      </c>
+      <c r="X55">
+        <v>0.248429848</v>
+      </c>
+      <c r="Y55">
+        <v>0.262175454</v>
+      </c>
+      <c r="Z55">
+        <v>0.3611832748860462</v>
+      </c>
+      <c r="AA55">
+        <v>6.872802999999998</v>
+      </c>
+      <c r="AB55">
+        <v>0.05349551169162379</v>
+      </c>
+      <c r="AC55">
+        <v>32.52721939217872</v>
+      </c>
+    </row>
+    <row r="56" spans="1:29">
       <c r="A56" s="1">
         <v>46068.60280657408</v>
       </c>
@@ -4393,14 +5254,29 @@
       <c r="U56">
         <v>607.834444791282</v>
       </c>
-      <c r="V56">
-        <v>0.8507007611323713</v>
-      </c>
-      <c r="W56" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="57" spans="1:23">
+      <c r="V56" t="b">
+        <v>1</v>
+      </c>
+      <c r="X56">
+        <v>0.248432072</v>
+      </c>
+      <c r="Y56">
+        <v>0.262169724</v>
+      </c>
+      <c r="Z56">
+        <v>0.3611806453569313</v>
+      </c>
+      <c r="AA56">
+        <v>6.868825999999999</v>
+      </c>
+      <c r="AB56">
+        <v>0.05352502710330367</v>
+      </c>
+      <c r="AC56">
+        <v>32.53435513177491</v>
+      </c>
+    </row>
+    <row r="57" spans="1:29">
       <c r="A57" s="1">
         <v>46068.60292231481</v>
       </c>
@@ -4464,14 +5340,29 @@
       <c r="U57">
         <v>609.5144019200826</v>
       </c>
-      <c r="V57">
-        <v>0.9171951433900267</v>
-      </c>
-      <c r="W57" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="58" spans="1:23">
+      <c r="V57" t="b">
+        <v>1</v>
+      </c>
+      <c r="X57">
+        <v>0.248422224</v>
+      </c>
+      <c r="Y57">
+        <v>0.262162084</v>
+      </c>
+      <c r="Z57">
+        <v>0.3611683259428063</v>
+      </c>
+      <c r="AA57">
+        <v>6.869929999999997</v>
+      </c>
+      <c r="AB57">
+        <v>0.05351496421926765</v>
+      </c>
+      <c r="AC57">
+        <v>32.61814140988155</v>
+      </c>
+    </row>
+    <row r="58" spans="1:29">
       <c r="A58" s="1">
         <v>46068.60303863426</v>
       </c>
@@ -4535,14 +5426,29 @@
       <c r="U58">
         <v>610.1205745799525</v>
       </c>
-      <c r="V58">
-        <v>1.184348671830666</v>
-      </c>
-      <c r="W58" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59" spans="1:23">
+      <c r="V58" t="b">
+        <v>1</v>
+      </c>
+      <c r="X58">
+        <v>0.248407294</v>
+      </c>
+      <c r="Y58">
+        <v>0.262161128</v>
+      </c>
+      <c r="Z58">
+        <v>0.3611573628581243</v>
+      </c>
+      <c r="AA58">
+        <v>6.876917000000006</v>
+      </c>
+      <c r="AB58">
+        <v>0.05346092603942893</v>
+      </c>
+      <c r="AC58">
+        <v>32.61761091275272</v>
+      </c>
+    </row>
+    <row r="59" spans="1:29">
       <c r="A59" s="1">
         <v>46068.6031549537</v>
       </c>
@@ -4606,14 +5512,29 @@
       <c r="U59">
         <v>610.7159777468647</v>
       </c>
-      <c r="V59">
-        <v>0.6007959570762184</v>
-      </c>
-      <c r="W59" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="60" spans="1:23">
+      <c r="V59" t="b">
+        <v>1</v>
+      </c>
+      <c r="X59">
+        <v>0.248388234</v>
+      </c>
+      <c r="Y59">
+        <v>0.262157626</v>
+      </c>
+      <c r="Z59">
+        <v>0.3611417113261698</v>
+      </c>
+      <c r="AA59">
+        <v>6.884695999999998</v>
+      </c>
+      <c r="AB59">
+        <v>0.05340040216900571</v>
+      </c>
+      <c r="AC59">
+        <v>32.61247882272012</v>
+      </c>
+    </row>
+    <row r="60" spans="1:29">
       <c r="A60" s="1">
         <v>46068.60327127315</v>
       </c>
@@ -4677,14 +5598,29 @@
       <c r="U60">
         <v>613.5877041987776</v>
       </c>
-      <c r="V60">
-        <v>1.853928510825953</v>
-      </c>
-      <c r="W60" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="61" spans="1:23">
+      <c r="V60" t="b">
+        <v>1</v>
+      </c>
+      <c r="X60">
+        <v>0.248386328</v>
+      </c>
+      <c r="Y60">
+        <v>0.262161446</v>
+      </c>
+      <c r="Z60">
+        <v>0.3611431734175997</v>
+      </c>
+      <c r="AA60">
+        <v>6.887558999999996</v>
+      </c>
+      <c r="AB60">
+        <v>0.05337919194236124</v>
+      </c>
+      <c r="AC60">
+        <v>32.75281583589932</v>
+      </c>
+    </row>
+    <row r="61" spans="1:29">
       <c r="A61" s="1">
         <v>46068.60338759259</v>
       </c>
@@ -4748,11 +5684,26 @@
       <c r="U61">
         <v>608.1989963178997</v>
       </c>
-      <c r="V61">
-        <v>2.696299345207509</v>
-      </c>
-      <c r="W61" t="b">
-        <v>1</v>
+      <c r="V61" t="b">
+        <v>1</v>
+      </c>
+      <c r="X61">
+        <v>0.248378388</v>
+      </c>
+      <c r="Y61">
+        <v>0.262162402</v>
+      </c>
+      <c r="Z61">
+        <v>0.3611384064979633</v>
+      </c>
+      <c r="AA61">
+        <v>6.892007</v>
+      </c>
+      <c r="AB61">
+        <v>0.05334527183313383</v>
+      </c>
+      <c r="AC61">
+        <v>32.44454078721753</v>
       </c>
     </row>
   </sheetData>
